--- a/data/daily/2026-09/2026-09-22.xlsx
+++ b/data/daily/2026-09/2026-09-22.xlsx
@@ -1170,14 +1170,89 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1267,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,110 +1367,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1425,52 +1425,152 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,24 +1578,24 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,129 +1603,29 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -2596,26 +2596,26 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16108</v>
+        <v>16109</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>빠른 배송과 안전한 포장 — 당일 배송이 아님에도 배송이 빠르고 포장이 안전함</t>
+          <t>피로 회복 효과 — 복용 후 컨디션 조절 및 에너지 충전에 도움을 줌</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>선물용으로 뛰어난 만족도 — 패키지가 깔끔하고 고급스러워 선물용으로 적합함</t>
+          <t>선물용 최적화 — 깔끔하고 고급스러운 패키지로 지인 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>우수한 휴대성과 간편함 — 한 병씩 가방에 넣고 다니며 간편하게 섭취 가능함</t>
+          <t>편리한 휴대성 — 한 병씩 개별 포장되어 가방에 넣고 다니며 먹기 편함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>선물용 쇼핑백 미동봉 — 기프트 에디션 구성임에도 종이가방이 포함되지 않음</t>
+          <t>쇼핑백 미동봉 — 기프트 에디션 구성에 종이 가방이 포함되어 있지 않음</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2659,21 +2659,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15438</v>
+        <v>15439</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>빠른 배송과 깔끔한 포장 — 배송이 빠르고 패키징 및 포 상태가 깔끔함</t>
+          <t>신속한 배송 서비스 — 주문 후 빠르게 제품을 받아볼 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>편리한 개별 포장 — 개별 포장되어 휴대하며 들고 다니기 용이함</t>
+          <t>깔끔한 패키징 — 깔끔한 포장과 1개 추가 증정 구성이 만족스러움</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>체력 증진 및 활력 효과 — 섭취 후 피로가 줄고 활력이 생기는 느낌임</t>
+          <t>개별 포장 편리성 — 개별로 포장되어 휴대하고 다니며 섭취하기 좋음</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2722,18 +2722,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>피로 회복 및 체력 증진 — 복용 후 피로감이 줄고 힘이 나는 효과가 있음</t>
+          <t>우수한 피로 개선 — 복용 후 피곤함이 줄어들고 기력 회복에 도움을 줌</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 명절 선물 — 케이스와 패키지가 고급스러워 선물용으로 적합함</t>
+          <t>고급스러운 패키지 — 명절 에디션 케이스가 예쁘고 고급스러워 선물로 좋음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>구매 후 가격 인하 — 구매 직후 제품 가격이 내려가 아쉬움이 남음</t>
+          <t>가격 변동의 아쉬움 — 제품을 구매한 직후 가격이 인하되어 아쉬움</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2781,17 +2781,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 섭취 후 피로가 해소되고 컨디션 회복에 도움이 됨</t>
+          <t>빠른 활력 충전 — 복용 후 컨디션이 빠르게 회복되고 에너지가 생김</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>용이한 알약 목넘김 — 알약 크기가 크지 않아 쉽게 넘길 수 있음</t>
+          <t>복용 편의성 제공 — 알약의 크기가 작아서 목을 넘길 때 걸림 없이 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>고급스러운 선물 구성 — 포장이 정성스럽고 고급스러워 선물용으로 제격임</t>
+          <t>정성스러운 포장 — 고급스럽게 포장되어 생일이나 명절 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2809,48 +2809,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10056171</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>8713</v>
+        <v>762</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>우수한 활력 및 피로 회복 — 섭취 후 활력이 생기고 피로감이 감소함</t>
+          <t>확실한 컨디션 회복 — 복용 시 피로가 개선되어 하루 종일 활력 유지가 가능함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>높은 가성비와 증정 혜택 — 가성비가 좋고 추가 증정 서비스 구성이 알참</t>
+          <t>뛰어난 가성비 — 알찬 제품 구성 대비 가격대가 합리적이라 만족스러움</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>편리한 휴대성 — 휴대하기 편하여 밖에서도 챙겨 먹기 좋음</t>
+          <t>섭취 및 휴대 간편 — 간편하게 필수 영양소를 챙길 수 있고 들고 다니기 쉬움</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2868,48 +2868,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/10056171</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>762</v>
+        <v>8714</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 — 섭취 당일 컨디션이 좋아지고 피로 회복에 도움 됨</t>
+          <t>탁월한 피로 개선 — 섭취 후 피로감이 줄고 일시적으로 에너지가 크게 도는 느낌을 줌</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>빠른 배송과 깔끔한 포장 — 배송이 빠르고 패키지가 깔끔하여 명절 선물로 좋음</t>
+          <t>우수한 가성비 — 가성비가 훌륭하며 서비스 증정 혜택도 만족스러움</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>간편한 섭취 및 휴대 — 필수 영양소를 간편하고 편리하게 챙기기 좋음</t>
+          <t>예쁜 포장과 편리함 — 패키지가 깔끔하고 휴대하기 편리하여 선물용으로 좋음</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -2958,17 +2958,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 맛있는 젤리 형태라 거부감 없이 섭취 가능함</t>
+          <t>맛있는 구미 형태 — 거부감 없는 맛있는 젤리 제형으로 꾸준히 먹기 편함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>물 없는 간편한 섭취 — 구미 타입이라 물 없이도 어디서나 간단히 먹기 좋음</t>
+          <t>간편한 섭취 방식 — 물 없이도 언제 어디서나 간편하게 섭취할 수 있음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>귀여운 포장과 사은품 — 포장이 귀엽고 사은품 구성 만족도가 높음</t>
+          <t>귀엽고 깔끔한 패키지 — 아기자기하고 깔끔하게 구성되어 가벼운 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3013,21 +3013,21 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>체감되는 활력 증진 — 복용한 날의 차이가 확연히 느껴질 정도로 활력이 돎</t>
+          <t>브랜드 높은 신뢰도 — 정관장 브랜드 제품이라 안심하고 섭취 및 선물이 가능함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 투명 케이스와 패키지가 고급스러워 선물용으로 적합함</t>
+          <t>간편한 올인원 제형 — 액상과 분말이 함께 있어 물 없이도 쉽게 먹을 수 있음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>물 필요 없는 올인원 타입 — 액상과 분말 올인원 타입으로 물 없이 복용함</t>
+          <t>뛰어난 활력 증진 — 피로 회복에 효과적이며 먹은 날과 안 먹은 날의 차이가 확실함</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3076,22 +3076,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>성별 맞춤 영양 구성 — 성별 선택이 가능하며 풍부한 영양 성분을 포함함</t>
+          <t>성별 맞춤 옵션 제공 — 바이탈 m/f 중 대상에 맞춰 선택하여 구매할 수 있음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 포장이 깔끔하고 정성스러워 선물받는 느낌이 큼</t>
+          <t>지속적인 활력 효과 — 꾸준히 섭취 시 피로가 덜하고 활력 상태가 오랫동안 유지됨</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>꾸준한 피로 회복 — 꾸준히 섭취 시 덜 피곤하고 체력 유지에 도움 됨</t>
+          <t>정성스러운 포장 상태 — 선물용으로 부족함이 없도록 포장이 깔끔하고 성의 있어 보임</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>부담스러운 알약 크기 — 기존 제품 대비 알약이 커서 삼키기 다소 힘듦</t>
+          <t>부담스러운 알약 크기 — 기존 제품 대비 정제의 크기가 다소 커서 삼키기 힘듦</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3139,18 +3139,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>빠른 배송과 정성스러운 포장 — 배송이 매우 빠르고 선물 패키징이 정성스럽고 고급스러움</t>
+          <t>우수한 활력 회복 — 복용 시 피로가 덜하고 컨디션 회복 속도가 빠름</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>간편한 복용과 빠른 피로 회복 — 하루 한 병으로 챙기기 편하며 피로 회복이 빠름</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>정성스러운 선물 패키지 — 고급스럽고 정성스러운 포장에 쇼핑백까지 동봉되어 선물하기 좋음</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>간편한 복용법 — 한 병에 액상과 정제가 같이 들어 있어 한 번에 먹기 편함</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>포장 개봉 스티커 훼손 — 밀봉 스티커가 떼어져 있거나 자국이 남아 있어 찝찝함</t>
+          <t>포장 스티커 오염 — 밀봉용 스티커가 뗐다 붙인 흔적이 있거나 손자국 및 이물질이 묻어 있음</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3198,22 +3202,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>정성스러운 예쁜 포장 — 보자기 및 틴케이스 포장이 고급스럽고 예쁨</t>
+          <t>화려하고 예쁜 포장 — 보자기, 오간자 포장과 틴케이스가 매우 고급스럽고 아름다움</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>비리지 않은 맛있는 섭취 — 콜라겐 특유의 비린 맛이 없고 맛있게 먹을 수 있음</t>
+          <t>비리지 않은 맛 — 콜라겐 특유의 비린 맛이 없고 맛있게 섭취할 수 있음</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>간편한 개별 앰플 포장 — 낱개 앰플 형태로 하나씩 따서 섭취하기 간편함</t>
+          <t>간편한 개별 앰플 — 낱개 앰플 형태로 제작되어 하나씩 꺼내 먹기 간편함</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>비싼 가격대 — 제품 가격이 점차 올라 가격 부담이 존재함</t>
+          <t>부담스러운 가격 상승 — 제품의 가격이 점차 올라 구매하기에 가격적 부담이 있음</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3261,22 +3265,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>부드러운 식감과 다양한 맛 — 뻑뻑함 없이 부드럽고 맛이 다양하여 질리지 않음</t>
+          <t>다양한 맛 구성 — 다채로운 메뉴로 구성되어 매일 먹어도 질리지 않음</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>알찬 구성과 높은 가성비 — 저렴한 가격 대비 수량이 넉넉하여 가성비가 뛰어남</t>
+          <t>부드럽고 맛있는 식감 — 닭가슴살 특유의 퍽퍽함이 덜하고 부드러우며 양념 맛이 좋음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>간편한 전자레인지 조리 — 전자레인지로 조리가 가능하여 간편하게 식단 관리를 함</t>
+          <t>훌륭한 가격 경쟁력 — 많은 수량 대비 저렴한 가격으로 가성비가 뛰어남</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>배송 시 제품 해동 — 배송 과정에서 상품이 전부 녹아서 도착함</t>
+          <t>배송 중 해동 발생 — 냉동 제품임에도 배송 도중 상품이 녹아서 도착함</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3320,22 +3324,26 @@
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 꾸준히 드시면 속이 편안해지고 더부룩함이 줄어듦</t>
+          <t>탁월한 소화 개선 — 섭취 후 속이 편안해지고 아침 배변에 도움을 줌</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>물 없이 섭취 가능한 제형 — 물 없이도 편하게 먹을 수 있으며 가격과 맛이 좋음</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>물 없이 섭취 가능 — 별도의 물 없이도 간편하게 가루째 섭취가 가능함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>합리적인 가격대 — 대용량 패키지와 사은품 증정 대비 가격이 저렴함</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>구매 제품의 맛 차이 — 기존에 복용하던 제품과 맛이 달라 아쉬움이 있음</t>
+          <t>기존 제품과 맛의 차이 — 이전에 섭취하던 유사 카무트 제품과 맛이 달라 생소함</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3344,7 +3352,7 @@
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3352,58 +3360,62 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)</t>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>86,800원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260921093919_9881af9e82944da586785c0fe2e5715a.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>1677</v>
+        <v>150</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>소화 및 변비 개선 효과 — 식후 소화 촉진 및 변비 증상 개선에 도움을 줌</t>
+          <t>높은 포만감 제공 — 제품 한 개만 먹어도 포만감이 오래 가 식사 대용으로 좋음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>합리적 가격과 사은품 혜택 — 특가 구매 시 가격 조건이 좋고 사은품 구성도 만족스러움</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>고급스러운 선물 포장 — 선물 포장이 고급스러워 부모님이나 지인 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+          <t>다채로운 종류 구성 — 한 달 분량 동안 다양한 맛을 고루 맛볼 수 있도록 구성됨</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>오배송 및 구성 누락 — 주문한 구성품과 다르게 제품이 중복되거나 누락되어 배송됨</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>포장 파손 및 터짐 — 팩 일부가 터져서 양념 소스가 새어 나오거나 진공 상태가 불량함</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3411,56 +3423,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>86,800원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260921093919_9881af9e82944da586785c0fe2e5715a.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>150</v>
+        <v>1679</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>뛰어난 포만감과 맛 — 한 개만 먹어도 포만감이 크고 맛이 뛰어남</t>
+          <t>소화 및 속 편함 효과 — 식후 섭취 시 소화가 잘되고 속을 편안하게 만들어 줌</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>다양하고 알찬 식단 구성 — 한 달 점심용으로 다양한 종류가 구성되어 있음</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>수량 및 구성 오배송 — 안내된 구성과 다르게 제품이 중복 또는 누락되어 배송됨</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>포장 훼손 및 소스 누출 — 포장이 헐렁하거나 팩이 터져 소스가 묻어옴</t>
-        </is>
-      </c>
+          <t>뛰어난 맛과 풍미 — 고소한 고구마 맛 등으로 효소 제품 중 맛이 가장 훌륭함</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>풍성한 사은품 혜택 — 사은품 증정이 많고 라이브 방송 혜택이 좋아 실속 있음</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
@@ -3505,18 +3513,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>속 편한 효과와 맛 — 식후 더부룩함이 감소하여 속이 편하고 맛도 고소함</t>
+          <t>말차의 맛있는 풍미 — 효소 특유의 냄새 없이 고소하고 맛있는 말차 맛을 구현함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>풍부한 에디션 혜택 구성 — 포토카드 및 단백질바 증정 등 혜택 구성이 알참</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>속 더부룩함 완화 — 섭취 후 위장의 소화 불량이 개선되고 속이 편안해짐</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>알찬 콜라보 구성 — 전용 포토카드와 단백질 바 사은품까지 주는 혜택 구성이 좋음</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>다소 지연된 배송 — 배송 진행 속도가 다소 늦어서 아쉬움이 있음</t>
+          <t>아쉬운 배송 속도 — 제품 배송이 완료되기까지 다소 지연되는 편임</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3564,17 +3576,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>비리지 않은 맛있는 맛 — 단백질 음료 특유의 비린 맛 없이 진하고 달콤함</t>
+          <t>깔끔하고 뛰어난 맛 — 단백질 음료 특유의 비린 맛과 텁텁함이 없이 부드럽고 달콤함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>속 더부룩함 없는 부드러움 — 목넘김이 부드럽고 마신 뒤 속이 더부룩하지 않음</t>
+          <t>우수한 속 편안함 — 분리유청 설계로 마신 후에도 더부룩함이 없고 편안함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>슬림한 패키지와 포만감 — 휴대하기 편하며 운동 후 가볍게 포만감을 채우기 좋음</t>
+          <t>든든한 포만감 형성 — 포만감이 느껴져 운동 전후나 가벼운 간식 대용으로 활용하기 좋음</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3623,18 +3635,18 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>예쁜 포장과 고급스러운 용기 — 포장이 예쁘고 용기 및 케이스 디자인이 고급스러움</t>
+          <t>공주풍의 예쁜 패키지 — 선물용으로 좋은 화사하고 아름다운 케이스와 오간자 포장임</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>부담 없는 상큼한 맛 — 비타민 음료처럼 상큼하고 맛있어 부담 없이 먹기 좋음</t>
+          <t>섭취 편한 앰플 형태 — 알약 섭취를 어려워하는 사람도 물과 함께 마시기 좋은 액상 형태임</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>약간 진한 농도 — 마시기에 앰플 농도가 조금 진하게 느껴질 수 있음</t>
+          <t>단기 효과 체감 불가 — 복용 기간이 짧아 피부 개선 등 눈에 띄는 효과를 바로 느끼기 힘듦</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -3682,17 +3694,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>체감되는 활력 증진 효과 — 초고함량 아르기닌 함유로 운동 및 피로 개선에 효과적임</t>
+          <t>압도적 아르기닌 함량 — 한 포당 6,200mg의 높은 아르기닌 함량으로 영양 보충에 확실함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>간편한 개별 포장 휴대 — 개별 포장되어 있어 휴대하기 쉽고 하루 1포로 간편 섭취함</t>
+          <t>강력한 피로 회복력 — 섭취 시 운동 수행 능력이 향상되고 지친 일상에 활력이 생김</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>쇼핑백 포함 고급 패키지 — 패키지 디자인이 고급스럽고 쇼핑백이 함께 증정됨</t>
+          <t>세련된 기프트 세트 — 블랙과 레드 톤의 고급 포장 및 쇼핑백 증정으로 선물용에 어울림</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3741,17 +3753,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>활력과 간 건강 알찬 세트 — 아르기닌과 밀크씨슬을 한 번에 챙길 수 있어 알참</t>
+          <t>이상적인 영양소 조합 — 활력을 돋우는 아르기닌과 간에 좋은 밀크씨슬이 알차게 구성됨</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 아침에 일어날 때 몸이 가볍고 활력 충전에 도움 됨</t>
+          <t>아침 기상 시 개운함 — 섭취 후 피로감이 확연히 덜하며 아침에 일어날 때 몸이 가벼워짐</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>고급 쇼핑백 증정 구성 — 쇼핑백이 증정되어 지인 선물용으로 전달하기 좋음</t>
+          <t>넉넉한 복용 용량 — 2개월 복용 분량으로 오랫동안 넉넉히 두고 건강 관리가 가능함</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3946,12 +3958,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>뉴트리포유</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -4003,12 +4015,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -4076,10 +4088,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16108</v>
+        <v>16109</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15438</v>
+        <v>15439</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3359</v>
@@ -4088,16 +4100,16 @@
         <v>789</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>8713</v>
+        <v>762</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>762</v>
+        <v>8714</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>6483</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>771</v>
@@ -4114,70 +4126,71 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>빠른 배송과 안전한 포장 — 당일 배송이 아님에도 배송이 빠르고 포장이 안전함
-선물용으로 뛰어난 만족도 — 패키지가 깔끔하고 고급스러워 선물용으로 적합함
-우수한 휴대성과 간편함 — 한 병씩 가방에 넣고 다니며 간편하게 섭취 가능함</t>
+          <t>피로 회복 효과 — 복용 후 컨디션 조절 및 에너지 충전에 도움을 줌
+선물용 최적화 — 깔끔하고 고급스러운 패키지로 지인 선물용으로 적합함
+편리한 휴대성 — 한 병씩 개별 포장되어 가방에 넣고 다니며 먹기 편함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>빠른 배송과 깔끔한 포장 — 배송이 빠르고 패키징 및 포 상태가 깔끔함
-편리한 개별 포장 — 개별 포장되어 휴대하며 들고 다니기 용이함
-체력 증진 및 활력 효과 — 섭취 후 피로가 줄고 활력이 생기는 느낌임</t>
+          <t>신속한 배송 서비스 — 주문 후 빠르게 제품을 받아볼 수 있음
+깔끔한 패키징 — 깔끔한 포장과 1개 추가 증정 구성이 만족스러움
+개별 포장 편리성 — 개별로 포장되어 휴대하고 다니며 섭취하기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 체력 증진 — 복용 후 피로감이 줄고 힘이 나는 효과가 있음
-고급스러운 명절 선물 — 케이스와 패키지가 고급스러워 선물용으로 적합함</t>
+          <t>우수한 피로 개선 — 복용 후 피곤함이 줄어들고 기력 회복에 도움을 줌
+고급스러운 패키지 — 명절 에디션 케이스가 예쁘고 고급스러워 선물로 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 섭취 후 피로가 해소되고 컨디션 회복에 도움이 됨
-용이한 알약 목넘김 — 알약 크기가 크지 않아 쉽게 넘길 수 있음
-고급스러운 선물 구성 — 포장이 정성스럽고 고급스러워 선물용으로 제격임</t>
+          <t>빠른 활력 충전 — 복용 후 컨디션이 빠르게 회복되고 에너지가 생김
+복용 편의성 제공 — 알약의 크기가 작아서 목을 넘길 때 걸림 없이 편함
+정성스러운 포장 — 고급스럽게 포장되어 생일이나 명절 선물용으로 적합함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>우수한 활력 및 피로 회복 — 섭취 후 활력이 생기고 피로감이 감소함
-높은 가성비와 증정 혜택 — 가성비가 좋고 추가 증정 서비스 구성이 알참
-편리한 휴대성 — 휴대하기 편하여 밖에서도 챙겨 먹기 좋음</t>
+          <t>확실한 컨디션 회복 — 복용 시 피로가 개선되어 하루 종일 활력 유지가 가능함
+뛰어난 가성비 — 알찬 제품 구성 대비 가격대가 합리적이라 만족스러움
+섭취 및 휴대 간편 — 간편하게 필수 영양소를 챙길 수 있고 들고 다니기 쉬움</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 — 섭취 당일 컨디션이 좋아지고 피로 회복에 도움 됨
-빠른 배송과 깔끔한 포장 — 배송이 빠르고 패키지가 깔끔하여 명절 선물로 좋음
-간편한 섭취 및 휴대 — 필수 영양소를 간편하고 편리하게 챙기기 좋음</t>
+          <t>탁월한 피로 개선 — 섭취 후 피로감이 줄고 일시적으로 에너지가 크게 도는 느낌을 줌
+우수한 가성비 — 가성비가 훌륭하며 서비스 증정 혜택도 만족스러움
+예쁜 포장과 편리함 — 패키지가 깔끔하고 휴대하기 편리하여 선물용으로 좋음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 맛있는 젤리 형태라 거부감 없이 섭취 가능함
-물 없는 간편한 섭취 — 구미 타입이라 물 없이도 어디서나 간단히 먹기 좋음
-귀여운 포장과 사은품 — 포장이 귀엽고 사은품 구성 만족도가 높음</t>
+          <t>맛있는 구미 형태 — 거부감 없는 맛있는 젤리 제형으로 꾸준히 먹기 편함
+간편한 섭취 방식 — 물 없이도 언제 어디서나 간편하게 섭취할 수 있음
+귀엽고 깔끔한 패키지 — 아기자기하고 깔끔하게 구성되어 가벼운 선물용으로 적합함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 활력 증진 — 복용한 날의 차이가 확연히 느껴질 정도로 활력이 돎
-고급스러운 패키지 디자인 — 투명 케이스와 패키지가 고급스러워 선물용으로 적합함
-물 필요 없는 올인원 타입 — 액상과 분말 올인원 타입으로 물 없이 복용함</t>
+          <t>브랜드 높은 신뢰도 — 정관장 브랜드 제품이라 안심하고 섭취 및 선물이 가능함
+간편한 올인원 제형 — 액상과 분말이 함께 있어 물 없이도 쉽게 먹을 수 있음
+뛰어난 활력 증진 — 피로 회복에 효과적이며 먹은 날과 안 먹은 날의 차이가 확실함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 영양 구성 — 성별 선택이 가능하며 풍부한 영양 성분을 포함함
-고급스러운 선물 포장 — 포장이 깔끔하고 정성스러워 선물받는 느낌이 큼
-꾸준한 피로 회복 — 꾸준히 섭취 시 덜 피곤하고 체력 유지에 도움 됨</t>
+          <t>성별 맞춤 옵션 제공 — 바이탈 m/f 중 대상에 맞춰 선택하여 구매할 수 있음
+지속적인 활력 효과 — 꾸준히 섭취 시 피로가 덜하고 활력 상태가 오랫동안 유지됨
+정성스러운 포장 상태 — 선물용으로 부족함이 없도록 포장이 깔끔하고 성의 있어 보임</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>빠른 배송과 정성스러운 포장 — 배송이 매우 빠르고 선물 패키징이 정성스럽고 고급스러움
-간편한 복용과 빠른 피로 회복 — 하루 한 병으로 챙기기 편하며 피로 회복이 빠름</t>
+          <t>우수한 활력 회복 — 복용 시 피로가 덜하고 컨디션 회복 속도가 빠름
+정성스러운 선물 패키지 — 고급스럽고 정성스러운 포장에 쇼핑백까지 동봉되어 선물하기 좋음
+간편한 복용법 — 한 병에 액상과 정제가 같이 들어 있어 한 번에 먹기 편함</t>
         </is>
       </c>
     </row>
@@ -4189,13 +4202,13 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>선물용 쇼핑백 미동봉 — 기프트 에디션 구성임에도 종이가방이 포함되지 않음</t>
+          <t>쇼핑백 미동봉 — 기프트 에디션 구성에 종이 가방이 포함되어 있지 않음</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>구매 후 가격 인하 — 구매 직후 제품 가격이 내려가 아쉬움이 남음</t>
+          <t>가격 변동의 아쉬움 — 제품을 구매한 직후 가격이 인하되어 아쉬움</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
@@ -4205,12 +4218,12 @@
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>부담스러운 알약 크기 — 기존 제품 대비 알약이 커서 삼키기 다소 힘듦</t>
+          <t>부담스러운 알약 크기 — 기존 제품 대비 정제의 크기가 다소 커서 삼키기 힘듦</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>포장 개봉 스티커 훼손 — 밀봉 스티커가 떼어져 있거나 자국이 남아 있어 찝찝함</t>
+          <t>포장 스티커 오염 — 밀봉용 스티커가 뗐다 붙인 흔적이 있거나 손자국 및 이물질이 묻어 있음</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4255,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>52,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>19,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>52,900원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -4425,12 +4438,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4482,12 +4495,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -4539,12 +4552,12 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -4623,13 +4636,13 @@
         <v>52</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1677</v>
+        <v>150</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>150</v>
+        <v>1679</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>98</v>
@@ -4655,68 +4668,70 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>정성스러운 예쁜 포장 — 보자기 및 틴케이스 포장이 고급스럽고 예쁨
-비리지 않은 맛있는 섭취 — 콜라겐 특유의 비린 맛이 없고 맛있게 먹을 수 있음
-간편한 개별 앰플 포장 — 낱개 앰플 형태로 하나씩 따서 섭취하기 간편함</t>
+          <t>화려하고 예쁜 포장 — 보자기, 오간자 포장과 틴케이스가 매우 고급스럽고 아름다움
+비리지 않은 맛 — 콜라겐 특유의 비린 맛이 없고 맛있게 섭취할 수 있음
+간편한 개별 앰플 — 낱개 앰플 형태로 제작되어 하나씩 꺼내 먹기 간편함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>부드러운 식감과 다양한 맛 — 뻑뻑함 없이 부드럽고 맛이 다양하여 질리지 않음
-알찬 구성과 높은 가성비 — 저렴한 가격 대비 수량이 넉넉하여 가성비가 뛰어남
-간편한 전자레인지 조리 — 전자레인지로 조리가 가능하여 간편하게 식단 관리를 함</t>
+          <t>다양한 맛 구성 — 다채로운 메뉴로 구성되어 매일 먹어도 질리지 않음
+부드럽고 맛있는 식감 — 닭가슴살 특유의 퍽퍽함이 덜하고 부드러우며 양념 맛이 좋음
+훌륭한 가격 경쟁력 — 많은 수량 대비 저렴한 가격으로 가성비가 뛰어남</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 꾸준히 드시면 속이 편안해지고 더부룩함이 줄어듦
-물 없이 섭취 가능한 제형 — 물 없이도 편하게 먹을 수 있으며 가격과 맛이 좋음</t>
+          <t>탁월한 소화 개선 — 섭취 후 속이 편안해지고 아침 배변에 도움을 줌
+물 없이 섭취 가능 — 별도의 물 없이도 간편하게 가루째 섭취가 가능함
+합리적인 가격대 — 대용량 패키지와 사은품 증정 대비 가격이 저렴함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>소화 및 변비 개선 효과 — 식후 소화 촉진 및 변비 증상 개선에 도움을 줌
-합리적 가격과 사은품 혜택 — 특가 구매 시 가격 조건이 좋고 사은품 구성도 만족스러움
-고급스러운 선물 포장 — 선물 포장이 고급스러워 부모님이나 지인 선물용으로 적합함</t>
+          <t>높은 포만감 제공 — 제품 한 개만 먹어도 포만감이 오래 가 식사 대용으로 좋음
+다채로운 종류 구성 — 한 달 분량 동안 다양한 맛을 고루 맛볼 수 있도록 구성됨</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 포만감과 맛 — 한 개만 먹어도 포만감이 크고 맛이 뛰어남
-다양하고 알찬 식단 구성 — 한 달 점심용으로 다양한 종류가 구성되어 있음</t>
+          <t>소화 및 속 편함 효과 — 식후 섭취 시 소화가 잘되고 속을 편안하게 만들어 줌
+뛰어난 맛과 풍미 — 고소한 고구마 맛 등으로 효소 제품 중 맛이 가장 훌륭함
+풍성한 사은품 혜택 — 사은품 증정이 많고 라이브 방송 혜택이 좋아 실속 있음</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 효과와 맛 — 식후 더부룩함이 감소하여 속이 편하고 맛도 고소함
-풍부한 에디션 혜택 구성 — 포토카드 및 단백질바 증정 등 혜택 구성이 알참</t>
+          <t>말차의 맛있는 풍미 — 효소 특유의 냄새 없이 고소하고 맛있는 말차 맛을 구현함
+속 더부룩함 완화 — 섭취 후 위장의 소화 불량이 개선되고 속이 편안해짐
+알찬 콜라보 구성 — 전용 포토카드와 단백질 바 사은품까지 주는 혜택 구성이 좋음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>비리지 않은 맛있는 맛 — 단백질 음료 특유의 비린 맛 없이 진하고 달콤함
-속 더부룩함 없는 부드러움 — 목넘김이 부드럽고 마신 뒤 속이 더부룩하지 않음
-슬림한 패키지와 포만감 — 휴대하기 편하며 운동 후 가볍게 포만감을 채우기 좋음</t>
+          <t>깔끔하고 뛰어난 맛 — 단백질 음료 특유의 비린 맛과 텁텁함이 없이 부드럽고 달콤함
+우수한 속 편안함 — 분리유청 설계로 마신 후에도 더부룩함이 없고 편안함
+든든한 포만감 형성 — 포만감이 느껴져 운동 전후나 가벼운 간식 대용으로 활용하기 좋음</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>예쁜 포장과 고급스러운 용기 — 포장이 예쁘고 용기 및 케이스 디자인이 고급스러움
-부담 없는 상큼한 맛 — 비타민 음료처럼 상큼하고 맛있어 부담 없이 먹기 좋음</t>
+          <t>공주풍의 예쁜 패키지 — 선물용으로 좋은 화사하고 아름다운 케이스와 오간자 포장임
+섭취 편한 앰플 형태 — 알약 섭취를 어려워하는 사람도 물과 함께 마시기 좋은 액상 형태임</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>체감되는 활력 증진 효과 — 초고함량 아르기닌 함유로 운동 및 피로 개선에 효과적임
-간편한 개별 포장 휴대 — 개별 포장되어 있어 휴대하기 쉽고 하루 1포로 간편 섭취함
-쇼핑백 포함 고급 패키지 — 패키지 디자인이 고급스럽고 쇼핑백이 함께 증정됨</t>
+          <t>압도적 아르기닌 함량 — 한 포당 6,200mg의 높은 아르기닌 함량으로 영양 보충에 확실함
+강력한 피로 회복력 — 섭취 시 운동 수행 능력이 향상되고 지친 일상에 활력이 생김
+세련된 기프트 세트 — 블랙과 레드 톤의 고급 포장 및 쇼핑백 증정으로 선물용에 어울림</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>활력과 간 건강 알찬 세트 — 아르기닌과 밀크씨슬을 한 번에 챙길 수 있어 알참
-확실한 피로 회복 효과 — 아침에 일어날 때 몸이 가볍고 활력 충전에 도움 됨
-고급 쇼핑백 증정 구성 — 쇼핑백이 증정되어 지인 선물용으로 전달하기 좋음</t>
+          <t>이상적인 영양소 조합 — 활력을 돋우는 아르기닌과 간에 좋은 밀크씨슬이 알차게 구성됨
+아침 기상 시 개운함 — 섭취 후 피로감이 확연히 덜하며 아침에 일어날 때 몸이 가벼워짐
+넉넉한 복용 용량 — 2개월 복용 분량으로 오랫동안 넉넉히 두고 건강 관리가 가능함</t>
         </is>
       </c>
     </row>
@@ -4728,35 +4743,35 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>비싼 가격대 — 제품 가격이 점차 올라 가격 부담이 존재함</t>
+          <t>부담스러운 가격 상승 — 제품의 가격이 점차 올라 구매하기에 가격적 부담이 있음</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>배송 시 제품 해동 — 배송 과정에서 상품이 전부 녹아서 도착함</t>
+          <t>배송 중 해동 발생 — 냉동 제품임에도 배송 도중 상품이 녹아서 도착함</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>구매 제품의 맛 차이 — 기존에 복용하던 제품과 맛이 달라 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>수량 및 구성 오배송 — 안내된 구성과 다르게 제품이 중복 또는 누락되어 배송됨
-포장 훼손 및 소스 누출 — 포장이 헐렁하거나 팩이 터져 소스가 묻어옴</t>
-        </is>
-      </c>
+          <t>기존 제품과 맛의 차이 — 이전에 섭취하던 유사 카무트 제품과 맛이 달라 생소함</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>오배송 및 구성 누락 — 주문한 구성품과 다르게 제품이 중복되거나 누락되어 배송됨
+포장 파손 및 터짐 — 팩 일부가 터져서 양념 소스가 새어 나오거나 진공 상태가 불량함</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>다소 지연된 배송 — 배송 진행 속도가 다소 늦어서 아쉬움이 있음</t>
+          <t>아쉬운 배송 속도 — 제품 배송이 완료되기까지 다소 지연되는 편임</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>약간 진한 농도 — 마시기에 앰플 농도가 조금 진하게 느껴질 수 있음</t>
+          <t>단기 효과 체감 불가 — 복용 기간이 짧아 피부 개선 등 눈에 띄는 효과를 바로 느끼기 힘듦</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
@@ -4785,12 +4800,12 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
+          <t>86,800원</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
           <t>46,900원</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>86,800원</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5005,7 +5020,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5013,12 +5028,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5028,41 +5043,41 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618637&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/xHnNEgPvPnLilc6RIN7P601618637_00_00xHnNEgPvPnLilc6RIN7P.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>421</v>
+        <v>2593</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>목이 편안해지는 효과 — 목 감기 기운이 있을 때 섭취 시 목이 편안해짐</t>
+          <t>훌륭한 커피 대체재 — 드립 커피 맛과 향이 나서 카페인을 줄이거나 커피 대신 마시기 좋음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>착한 가격과 가성비 — 저렴한 가격대로 구매할 수 있어 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>편리한 섭취 방식 — 간편하게 먹을 수 있어 상비용으로 구매하기 좋음</t>
-        </is>
-      </c>
+          <t>간편한 다이어트 관리 — 폭식한 날 가볍게 타 먹으며 기분 좋게 체지방 관리를 시도함</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>한 입 크기의 적은 양 — 한 입이면 다 마셔서 양에 대한 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>과도하게 쓴 맛 — 제품 특유의 맛이 너무 써서 단독으로 섭취하기에 다소 부담스러움</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>다이어트 효과 미비 — 꾸준히 마셔도 체지방 감소 등의 직접적인 효과는 느끼기 어려움</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
@@ -5076,48 +5091,56 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032640075&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/0RECqyOK2V8qTztn2K7E032640075_00_000RECqyOK2V8qTztn2K7E.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>1021</v>
+        <v>70</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>착한 가격과 가성비 — 가격을 고려했을 때 품질과 활용도가 뛰어남</t>
+          <t>즉각적인 구강 상쾌함 — 캡슐을 터트리는 순간 입안의 텁텁함과 구취가 사라지고 개운해짐</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>편리한 포 형태 포장 — 개별 포장 형태로 섭취나 요리에 활용하기 편리함</t>
+          <t>착한 가격과 휴대성 — 합리적인 가격에 간편히 들고 다니며 필요할 때 섭취할 수 있음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>캡슐 내 소량의 내용물 — 한 알당 내용물이 적게 느껴져 완전한 상쾌함을 위해 여러 알이 필요함</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 자극 — 민트향 등으로 인해 다소 맵게 느껴지거나 개인 입맛에 맞지 않을 수 있음</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
@@ -5131,12 +5154,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5146,34 +5169,38 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260106/ifUNcDpBRic8ZZffJeay031930043_00_03ifUNcDpBRic8ZZffJeay.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1188</v>
+        <v>1705</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>관절 통증 완화 효과 — 복용 후 무릎 관절 통증 완화에 도움이 됨</t>
+          <t>빠른 수면 유도 효과 — 복용 후 단시간 내에 졸음이 찾아와 잠드는 데 큰 도움을 줌</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>부담 없는 알뜰 가성비 — 저렴한 가격으로 지속적으로 구매하기 부담 없음</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>수면의 질 대폭 개선 — 복용 시 깊은 잠을 잘 수 있게 유도하고 새벽에 깨는 현상을 줄여줌</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>저렴한 가성비 획득 — 다이소 특유의 저렴한 비용으로 수면 케어 제품을 부담 없이 체험함</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>소용량 규격의 아쉬움 — 30정 단위 포장이라 더 많은 대용량 구성을 원함</t>
+          <t>다소 아쉬운 함량 — 한 정당 함량이 2mg으로 적어 고함량을 원하는 이에게는 약할 수 있음</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -5190,12 +5217,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>자연관 정성담은 배도라지스틱 12포</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5205,39 +5232,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762093&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260508/SdledEzpIdjdFFQW6W8g901762093_00_00SdledEzpIdjdFFQW6W8g.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>882</v>
+        <v>3775</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>기관지 보호 효과 — 추운 날씨나 목 건강 관리를 위해 먹기 적합함</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>저렴한 알뜰 가성비 — 가격 대비 구성이 훌륭하여 자주 구매하기 좋음</t>
-        </is>
-      </c>
+          <t>기대 이상의 제품력 — 가격 대비 복용 만족도가 높으며 일상에서 챙겨 먹기 유용함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>지극히 평범한 효능 — 특별히 뛰어난 개선점을 느끼지 못하고 무난하게 느껴짐</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5245,12 +5272,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5260,37 +5287,37 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/2rLyPRrrXXN6XdvBMjj5913624075_00_002rLyPRrrXXN6XdvBMjj5.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1012</v>
+        <v>3423</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>톡 털어 먹는 간편함 — 그냥 털어 먹거나 물에 타 먹기 편하고 맛도 좋음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>몸이 가벼워지는 느낌 — 꾸준히 복용 시 몸이 한결 가볍게 느껴짐</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>저렴한 가성비 — 저렴한 가격에 부담 없이 지속 복용 가능함</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>멀티 복합 영양 배합 — 칼슘과 마그네슘, 비타민D를 한 알에 간편하게 섭취할 수 있어 유용함</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>포장 비닐 탈착 불량 — 알약을 꺼낼 때 포장 비닐이 같이 뜯겨 나와 정제에 눌어붙는 현상이 있음</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>아쉬운 주성분 함량 — 단일 고용량 영양제와 비교했을 때 개별 성분의 함량 수치가 다소 낮음</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -5304,48 +5331,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 2030 에너지 올인원 12포 12일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991013&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/qbG957X6MlxUkPfY6MmA033991013_00_00qbG957X6MlxUkPfY6MmA.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260922/2diYV2S85V8WH0UA5lRP030086178_00_002diYV2S85V8WH0UA5lRP.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>52</v>
+        <v>836</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 — 복용 후 피로감이 크게 줄어들고 몸이 좋아짐</t>
+          <t>훌륭한 가성비 충족 — 매우 저렴한 가격에 맛있는 비타민C를 확보하여 섭취 가능함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>여행용 휴대 편의성 — 포 포장이라 여행 시 휴대하여 챙기기 용이함</t>
+          <t>맛있는 분말 섭취 — 레몬 맛이 맛있어 물 없이도 간식처럼 쉽게 가루째 섭취할 수 있음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>저렴한 가성비 — 가격 대비 성능과 만족도가 우수함</t>
+          <t>소량 포장 휴대성 — 10개입 소량 단위 구성으로 제작되어 단기 여행 시 지참하기 수월함</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -5390,19 +5417,23 @@
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>6594</v>
+        <v>6602</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>약사 추천 및 혈압 관리 — 혈압 조절 및 고혈압 관리를 위해 복용하기 적합함</t>
+          <t>적당한 정제 크기 — 알약의 사이즈가 크지 않고 아담하여 목 넘김 시 부담이 거의 없음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 재구매 — 저렴하여 부담 없이 꾸준히 재구매하여 복용함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>위생적인 개별 포장 — 낱개로 개별 포장되어 있어 공기 차단에 우수하고 휴대하기 편리함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>합리적인 가성비 — 대웅제약 브랜드 신뢰도 대비 가격이 매우 저렴하게 출시됨</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -5418,12 +5449,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오브맘 기억력 그린라이트 30일분</t>
+          <t>유한양행 프리바이오틱스 스틱 40포 20일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5433,43 +5464,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624077&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651647&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/l4wgtUT4J6F7QmnnIAOw913624077_00_00l4wgtUT4J6F7QmnnIAOw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/3lk29dAMMktUiVesbwgQ600651647_00_003lk29dAMMktUiVesbwgQ.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>623</v>
+        <v>435</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>우수한 알뜰 가성비 — 가격이 매우 저렴하여 만족도가 높음</t>
+          <t>배변 활동 개선력 — 꾸준히 섭취 시 변비 증상을 가라앉히는 데 도움을 줌</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>부모님 건강 선물용 — 나이드신 부모님께 사드리기 좋은 제품임</t>
+          <t>저렴한 구매 단가 — 유한양행 브랜드 제품을 다이소 채널에서 무척 실속 있게 구매 가능함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>느린 효과 체감 — 복용 기간에 비해 즉각적인 효과 체감은 미미함</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5477,51 +5504,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>동국제약 마데카 저분자 콜라겐C</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910603&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250530/iFPtDwREEwh2EwWoojJJ610910603_00_01iFPtDwREEwh2EwWoojJJ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>671</v>
+        <v>2382</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>타사 대비 압도적 가성비 — 저렴한 가격에 저분자 콜라겐, 비타민C, 엘라스틴을 포함함</t>
+          <t>체감 가능한 철분 효과 — 병원 정밀 검사 시 철분 수치가 정상 범위로 유지되는 데 기여함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>초저분자 콜라겐 함유 — 흡수율이 높은 초저분자 콜라겐이 사용됨</t>
+          <t>매우 저렴한 가격대 — 대웅제약 철분 제품을 다이소 특유의 압도적인 가성비로 이용 가능함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>대체당 첨가 및 비린 향 — 대체당이 첨가되어 있고 특유의 비린 냄새가 약간 남음</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -5536,47 +5559,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+          <t>대웅제약 베르베린 500 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=025575127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000206&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/VsX5iaJon2xHHTs8AQHv025575127_00_01VsX5iaJon2xHHTs8AQHv.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/MYOwtzQEETqQTroQjYz5600000206_00_00MYOwtzQEETqQTroQjYz5.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>874</v>
+        <v>798</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>붓기 완화 도움 — 매일 복용 시 붓기 완화 및 컨디션 유지에 도움이 됨</t>
+          <t>혈당 완화 체감 — 꾸준히 섭취하면서 공복 혈당 수치가 점차 내려가는 것을 느낌</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>브랜드 신뢰도 — 셀트리온 제조 제품이라 신뢰하고 구매함</t>
+          <t>편리한 하루 복용 — 하루 한 번 한 정만 간편히 챙기면 되어 매일 유지하기 수월함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>정제의 강한 쓴맛 — 알약 자체의 맛이 너무 써서 제대로 삼키기조차 어려움</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5691,47 +5718,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5748,52 +5775,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>홀베리</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>판티오</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>대웅제약</t>
         </is>
       </c>
     </row>
@@ -5805,32 +5832,32 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>자연관 정성담은 배도라지스틱 12포</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 2030 에너지 올인원 12포 12일분</t>
+          <t>홀베리 레몬 비타C 500 10개입</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -5840,17 +5867,17 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 기억력 그린라이트 30일분</t>
+          <t>유한양행 프리바이오틱스 스틱 40포 20일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 마데카 저분자 콜라겐C</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+          <t>대웅제약 베르베린 500 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5891,7 @@
         <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
@@ -5873,16 +5900,16 @@
         <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
@@ -5898,34 +5925,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>421</v>
+        <v>2593</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1021</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1188</v>
+        <v>1705</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>882</v>
+        <v>3775</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1012</v>
+        <v>3423</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>52</v>
+        <v>836</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>6594</v>
+        <v>6602</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>623</v>
+        <v>435</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>671</v>
+        <v>2382</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>874</v>
+        <v>798</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -5936,69 +5963,67 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>목이 편안해지는 효과 — 목 감기 기운이 있을 때 섭취 시 목이 편안해짐
-착한 가격과 가성비 — 저렴한 가격대로 구매할 수 있어 만족도가 높음
-편리한 섭취 방식 — 간편하게 먹을 수 있어 상비용으로 구매하기 좋음</t>
+          <t>훌륭한 커피 대체재 — 드립 커피 맛과 향이 나서 카페인을 줄이거나 커피 대신 마시기 좋음
+간편한 다이어트 관리 — 폭식한 날 가볍게 타 먹으며 기분 좋게 체지방 관리를 시도함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>착한 가격과 가성비 — 가격을 고려했을 때 품질과 활용도가 뛰어남
-편리한 포 형태 포장 — 개별 포장 형태로 섭취나 요리에 활용하기 편리함</t>
+          <t>즉각적인 구강 상쾌함 — 캡슐을 터트리는 순간 입안의 텁텁함과 구취가 사라지고 개운해짐
+착한 가격과 휴대성 — 합리적인 가격에 간편히 들고 다니며 필요할 때 섭취할 수 있음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>관절 통증 완화 효과 — 복용 후 무릎 관절 통증 완화에 도움이 됨
-부담 없는 알뜰 가성비 — 저렴한 가격으로 지속적으로 구매하기 부담 없음</t>
+          <t>빠른 수면 유도 효과 — 복용 후 단시간 내에 졸음이 찾아와 잠드는 데 큰 도움을 줌
+수면의 질 대폭 개선 — 복용 시 깊은 잠을 잘 수 있게 유도하고 새벽에 깨는 현상을 줄여줌
+저렴한 가성비 획득 — 다이소 특유의 저렴한 비용으로 수면 케어 제품을 부담 없이 체험함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>기관지 보호 효과 — 추운 날씨나 목 건강 관리를 위해 먹기 적합함
-저렴한 알뜰 가성비 — 가격 대비 구성이 훌륭하여 자주 구매하기 좋음</t>
+          <t>기대 이상의 제품력 — 가격 대비 복용 만족도가 높으며 일상에서 챙겨 먹기 유용함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>톡 털어 먹는 간편함 — 그냥 털어 먹거나 물에 타 먹기 편하고 맛도 좋음
-몸이 가벼워지는 느낌 — 꾸준히 복용 시 몸이 한결 가볍게 느껴짐
-저렴한 가성비 — 저렴한 가격에 부담 없이 지속 복용 가능함</t>
+          <t>멀티 복합 영양 배합 — 칼슘과 마그네슘, 비타민D를 한 알에 간편하게 섭취할 수 있어 유용함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 — 복용 후 피로감이 크게 줄어들고 몸이 좋아짐
-여행용 휴대 편의성 — 포 포장이라 여행 시 휴대하여 챙기기 용이함
-저렴한 가성비 — 가격 대비 성능과 만족도가 우수함</t>
+          <t>훌륭한 가성비 충족 — 매우 저렴한 가격에 맛있는 비타민C를 확보하여 섭취 가능함
+맛있는 분말 섭취 — 레몬 맛이 맛있어 물 없이도 간식처럼 쉽게 가루째 섭취할 수 있음
+소량 포장 휴대성 — 10개입 소량 단위 구성으로 제작되어 단기 여행 시 지참하기 수월함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>약사 추천 및 혈압 관리 — 혈압 조절 및 고혈압 관리를 위해 복용하기 적합함
-뛰어난 가성비와 재구매 — 저렴하여 부담 없이 꾸준히 재구매하여 복용함</t>
+          <t>적당한 정제 크기 — 알약의 사이즈가 크지 않고 아담하여 목 넘김 시 부담이 거의 없음
+위생적인 개별 포장 — 낱개로 개별 포장되어 있어 공기 차단에 우수하고 휴대하기 편리함
+합리적인 가성비 — 대웅제약 브랜드 신뢰도 대비 가격이 매우 저렴하게 출시됨</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>우수한 알뜰 가성비 — 가격이 매우 저렴하여 만족도가 높음
-부모님 건강 선물용 — 나이드신 부모님께 사드리기 좋은 제품임</t>
+          <t>배변 활동 개선력 — 꾸준히 섭취 시 변비 증상을 가라앉히는 데 도움을 줌
+저렴한 구매 단가 — 유한양행 브랜드 제품을 다이소 채널에서 무척 실속 있게 구매 가능함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>타사 대비 압도적 가성비 — 저렴한 가격에 저분자 콜라겐, 비타민C, 엘라스틴을 포함함
-초저분자 콜라겐 함유 — 흡수율이 높은 초저분자 콜라겐이 사용됨</t>
+          <t>체감 가능한 철분 효과 — 병원 정밀 검사 시 철분 수치가 정상 범위로 유지되는 데 기여함
+매우 저렴한 가격대 — 대웅제약 철분 제품을 다이소 특유의 압도적인 가성비로 이용 가능함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>붓기 완화 도움 — 매일 복용 시 붓기 완화 및 컨디션 유지에 도움이 됨
-브랜드 신뢰도 — 셀트리온 제조 제품이라 신뢰하고 구매함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>혈당 완화 체감 — 꾸준히 섭취하면서 공복 혈당 수치가 점차 내려가는 것을 느낌
+편리한 하루 복용 — 하루 한 번 한 정만 간편히 챙기면 되어 매일 유지하기 수월함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -6006,30 +6031,41 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>한 입 크기의 적은 양 — 한 입이면 다 마셔서 양에 대한 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>과도하게 쓴 맛 — 제품 특유의 맛이 너무 써서 단독으로 섭취하기에 다소 부담스러움
+다이어트 효과 미비 — 꾸준히 마셔도 체지방 감소 등의 직접적인 효과는 느끼기 어려움</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>캡슐 내 소량의 내용물 — 한 알당 내용물이 적게 느껴져 완전한 상쾌함을 위해 여러 알이 필요함
+호불호 갈리는 자극 — 민트향 등으로 인해 다소 맵게 느껴지거나 개인 입맛에 맞지 않을 수 있음</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>소용량 규격의 아쉬움 — 30정 단위 포장이라 더 많은 대용량 구성을 원함</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+          <t>다소 아쉬운 함량 — 한 정당 함량이 2mg으로 적어 고함량을 원하는 이에게는 약할 수 있음</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>지극히 평범한 효능 — 특별히 뛰어난 개선점을 느끼지 못하고 무난하게 느껴짐</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>포장 비닐 탈착 불량 — 알약을 꺼낼 때 포장 비닐이 같이 뜯겨 나와 정제에 눌어붙는 현상이 있음
+아쉬운 주성분 함량 — 단일 고용량 영양제와 비교했을 때 개별 성분의 함량 수치가 다소 낮음</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>느린 효과 체감 — 복용 기간에 비해 즉각적인 효과 체감은 미미함</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>대체당 첨가 및 비린 향 — 대체당이 첨가되어 있고 특유의 비린 냄새가 약간 남음</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>정제의 강한 쓴맛 — 알약 자체의 맛이 너무 써서 제대로 삼키기조차 어려움</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6044,47 +6080,47 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6299,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6271,27 +6307,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>그린몬스터</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000172168&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017216854ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6306,7 +6342,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6314,27 +6350,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 (1개월분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>129,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000207974&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020797409ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -6349,7 +6385,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6357,45 +6393,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>탄탄 젤리 더블컷 다이어트 모음전(오리지널/포켓몬 에디션)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>탄탄</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8,990원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244912&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024491247ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6203</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>야식 및 디저트 대용 — 과식 후나 밤에 디저트가 당길 때 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>다이어트 보조 효과 — 운동과 병행 시 맛있는 다이어트 보조 시너지를 냄</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -6404,7 +6428,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6412,50 +6436,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
+          <t>탄탄 젤리 더블컷 다이어트 모음전(오리지널/포켓몬 에디션)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>탄탄</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>8,990원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225906&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244912&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022590605ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6809</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>체감되는 피로 회복 — 섭취 후 피로도 체감이 확연히 줄어들고 몸이 가뿐해짐</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>고용량 3000mg 섭취 — 가루 형태로 고용량 비타민C를 간편하게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>온 가족 장기 복용 — 온 가족이 몇 년째 꾸준히 챙겨 먹는 필수 영양제임</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024491247ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -6463,7 +6471,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6471,50 +6479,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24,700원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>9279</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>탁월한 붓기 관리 — 야식이나 맵단짠 음식 섭취 후 붓기 관리에 효과적임</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>편리한 휴대성 — 작은 액상 포 형태로 물 없이 어디서나 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>상큼하고 맛있는 포도맛 — 한약 맛 부담 없이 거부감 없이 맛있게 먹기 좋음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -6522,7 +6514,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6530,50 +6522,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>24,700원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>24514</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>장 건강과 면역 케어 — 아침 공복에 복용 시 장 건강과 면역력 증진에 효과적임</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1일 1캡슐 복용 — 1일 1캡슐 구성으로 미지근한 물과 매일 먹기 간편함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1+1 기획 및 증정 구성 — 더블 기획 및 추가 증정으로 넉넉하게 복용 가능함</t>
-        </is>
-      </c>
+        <v>9288</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -6581,7 +6561,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6589,34 +6569,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>고려은단 식물성 알티지 오메가3 30캡슐 (30일분)</t>
+          <t>비타바움 비타민B12 40000% 플러스 브이 컴플렉스 8 (30병입) (1개월분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>비타바움</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>95,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000201188&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000251282&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020118813ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025128206ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>4912</v>
+        <v>3</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -6628,7 +6608,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6636,41 +6616,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[9월 올영픽/급찐급빠] 칼로 스탑/컨트롤 PLUS 15포+15포 (+폼폼푸린 키링) / 더블기획 3종</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>19,400원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000243670&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>여성 질 건강 집중 케어 — 공복에 챙겨 먹는 질유산균으로 건강한 루틴을 형성함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>키링 및 증정품 구성 — 철분 혜택 및 캐릭터 키링 등 구성품이 만족스러움</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024367012ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12036</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -6679,7 +6655,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6687,31 +6663,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
+          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>아임비타</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18,700원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249166&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993425ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A000000249166123ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10982</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -6722,7 +6702,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6730,34 +6710,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
+          <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CJ이너비</t>
+          <t>그린몬스터</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11,400원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000264048&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000172168&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026404813ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017216854ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>체감되는 보장 유산균 — 섭취 중단 시 바로 증상 차이가 나며 여성 건강 관리에 큰 보탬이 됨</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>안전한 코팅 공법 — 듀라벡 코팅 기술을 적용하여 생 유산균을 안정적으로 장까지 보냄</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>합리적인 경제성 — 고가 제품 대비 품질 차이가 크지 않아 가격 부담 없이 정착하기 좋음</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -6873,52 +6865,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -6930,52 +6922,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>탄탄</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>판도라</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>비타바움</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>칼로(Kalo)</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>아임비타</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>그린몬스터</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>빌드</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>탄탄</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>CJ이너비</t>
         </is>
       </c>
     </row>
@@ -6987,52 +6979,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 (1개월분)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>탄탄 젤리 더블컷 다이어트 모음전(오리지널/포켓몬 에디션)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>비타바움 비타민B12 40000% 플러스 브이 컴플렉스 8 (30병입) (1개월분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/급찐급빠] 칼로 스탑/컨트롤 PLUS 15포+15포 (+폼폼푸린 키링) / 더블기획 3종</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>탄탄 젤리 더블컷 다이어트 모음전(오리지널/포켓몬 에디션)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>고려은단 식물성 알티지 오메가3 30캡슐 (30일분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
         </is>
       </c>
     </row>
@@ -7044,23 +7036,21 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
@@ -7071,23 +7061,21 @@
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="n">
-        <v>6203</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>6809</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>9279</v>
-      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="n">
-        <v>24514</v>
+        <v>9288</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>4912</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>12036</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>10982</v>
+      </c>
       <c r="L7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -7098,42 +7086,20 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>야식 및 디저트 대용 — 과식 후나 밤에 디저트가 당길 때 먹기 좋음
-다이어트 보조 효과 — 운동과 병행 시 맛있는 다이어트 보조 시너지를 냄</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>체감되는 피로 회복 — 섭취 후 피로도 체감이 확연히 줄어들고 몸이 가뿐해짐
-고용량 3000mg 섭취 — 가루 형태로 고용량 비타민C를 간편하게 섭취 가능함
-온 가족 장기 복용 — 온 가족이 몇 년째 꾸준히 챙겨 먹는 필수 영양제임</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>탁월한 붓기 관리 — 야식이나 맵단짠 음식 섭취 후 붓기 관리에 효과적임
-편리한 휴대성 — 작은 액상 포 형태로 물 없이 어디서나 먹기 편함
-상큼하고 맛있는 포도맛 — 한약 맛 부담 없이 거부감 없이 맛있게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>장 건강과 면역 케어 — 아침 공복에 복용 시 장 건강과 면역력 증진에 효과적임
-1일 1캡슐 복용 — 1일 1캡슐 구성으로 미지근한 물과 매일 먹기 간편함
-1+1 기획 및 증정 구성 — 더블 기획 및 추가 증정으로 넉넉하게 복용 가능함</t>
-        </is>
-      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>여성 질 건강 집중 케어 — 공복에 챙겨 먹는 질유산균으로 건강한 루틴을 형성함
-키링 및 증정품 구성 — 철분 혜택 및 캐릭터 키링 등 구성품이 만족스러움</t>
-        </is>
-      </c>
+      <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>체감되는 보장 유산균 — 섭취 중단 시 바로 증상 차이가 나며 여성 건강 관리에 큰 보탬이 됨
+안전한 코팅 공법 — 듀라벡 코팅 기술을 적용하여 생 유산균을 안정적으로 장까지 보냄
+합리적인 경제성 — 고가 제품 대비 품질 차이가 크지 않아 가격 부담 없이 정착하기 좋음</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7160,52 +7126,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>129,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>8,990원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>24,700원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>95,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>19,400원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
           <t>16,900원</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>18,900원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>8,990원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>24,700원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>30,400원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>9,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>18,700원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>11,400원</t>
         </is>
       </c>
     </row>
@@ -7357,10 +7323,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -7369,7 +7335,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -7379,10 +7345,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
@@ -7391,7 +7357,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7423,16 +7389,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -7441,7 +7407,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7454,16 +7420,16 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7473,13 +7439,13 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7507,7 +7473,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7517,13 +7483,13 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
